--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
         <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4637,10 +4637,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10706,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10944,10 +10944,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15704,10 +15704,10 @@
         <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="M142" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N142" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17367,7 +17367,7 @@
         <v>1.95</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="M155" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="N155" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G165" t="n">

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>2.8</v>
       </c>
       <c r="M35" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
         <v>3.95</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
         <v>3.95</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.02</v>
+        <v>14</v>
       </c>
       <c r="M134" t="n">
-        <v>3.75</v>
+        <v>8.5</v>
       </c>
       <c r="N134" t="n">
-        <v>3.45</v>
+        <v>1.16</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,16 +16412,16 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD134" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G165" t="n">

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI166"/>
+  <dimension ref="A1:AI125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46012.375</v>
+        <v>46012.39583333334</v>
       </c>
     </row>
     <row r="19">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46012.39583333334</v>
+        <v>46012.40972222222</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46012.40972222222</v>
+        <v>46012.41666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46012.41666666666</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46012.41666666666</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46012.41666666666</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="32">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,76 +5300,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="42">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="45">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="46">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="47">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="48">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="49">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="50">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46012.49305555555</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="51">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="80">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="81">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="82">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="83">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="84">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="85">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="86">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10706,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="87">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,16 +10819,16 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="88">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="89">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="AI89" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="90">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="AI90" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="91">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11319,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="92">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11438,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="AI92" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="93">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11557,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="AI93" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="94">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.55208333334</v>
       </c>
     </row>
     <row r="95">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="AI95" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="96">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11914,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="97">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12033,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="AI97" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="98">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12152,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="99">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="AI99" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="100">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12372,10 +12372,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="101">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12509,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="102">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12628,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="103">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.57291666666</v>
       </c>
     </row>
     <row r="104">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AI104" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="105">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="107">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="108">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="109">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="111">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="112">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="113">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="114">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="115">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.64583333334</v>
       </c>
     </row>
     <row r="116">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.66666666666</v>
       </c>
     </row>
     <row r="117">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="118">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="119">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="M119" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N119" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.69791666666</v>
       </c>
     </row>
     <row r="120">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14770,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="121">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="122">
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="123">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="124">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="125">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15365,4885 +15365,6 @@
         <v>0</v>
       </c>
       <c r="AI125" s="3" t="n">
-        <v>46012.54166666666</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Spain Segunda División RFEF Group 2</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Real Zaragoza II</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Beasain</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" s="3" t="n">
-        <v>46012.54166666666</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Italy Serie B</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Mantova</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M127" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N127" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI127" s="3" t="n">
-        <v>46012.55208333334</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group B</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Forlì</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group C</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Monopoli</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Potenza Calcio</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group A</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Novara</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Ospitaletto</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI130" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group A</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Giana Erminio</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Cittadella</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI131" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group A</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Lecco</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Pergolettese</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Hungary NB I</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Debrecen</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Várda SE</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Germany Bundesliga</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Bayern München</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>14</v>
-      </c>
-      <c r="M134" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N135" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" s="3" t="n">
-        <v>46012.5625</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Rijeka</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Gorica</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" s="3" t="n">
-        <v>46012.57291666666</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Cyprus First Division</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Digenis Ypsonas</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Apollon</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" s="3" t="n">
-        <v>46012.58333333334</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M138" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N138" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" s="3" t="n">
-        <v>46012.58333333334</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Turkey Süper Lig</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Galatasaray</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Kasımpaşa</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" s="3" t="n">
-        <v>46012.58333333334</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Turkey Süper Lig</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Göztepe</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Samsunspor</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" s="3" t="n">
-        <v>46012.58333333334</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Cyprus First Division</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Paphos</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>APOEL</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" t="n">
-        <v>0</v>
-      </c>
-      <c r="X141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI141" s="3" t="n">
-        <v>46012.58333333334</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Spain Segunda División</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Granada CF</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Albacete Balompié</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Belgium Pro League</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Royal Antwerp FC</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>RSC Anderlecht</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="M143" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N143" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI143" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Spain Segunda División</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Burgos CF</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Real Zaragoza</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI144" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Al Kholood</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI145" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Al Najma</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Al Nassr</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>0</v>
-      </c>
-      <c r="U146" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI146" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Elche CF</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI147" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>PAOK</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Panathinaikos</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L148" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M148" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N148" t="n">
-        <v>4</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI148" s="3" t="n">
-        <v>46012.60416666666</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>CD Tondela</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Casa Pia</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI149" s="3" t="n">
-        <v>46012.625</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>FC Penafiel</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI150" s="3" t="n">
-        <v>46012.625</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>FCSB</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Rapid Bucureşti</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M151" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N151" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" t="n">
-        <v>0</v>
-      </c>
-      <c r="V151" t="n">
-        <v>0</v>
-      </c>
-      <c r="W151" t="n">
-        <v>0</v>
-      </c>
-      <c r="X151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI151" s="3" t="n">
-        <v>46012.625</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Belgium First Division B</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AS Eupen</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Olympic Charleroi</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" t="n">
-        <v>0</v>
-      </c>
-      <c r="V152" t="n">
-        <v>0</v>
-      </c>
-      <c r="W152" t="n">
-        <v>0</v>
-      </c>
-      <c r="X152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI152" s="3" t="n">
-        <v>46012.63541666666</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Belgium Pro League</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>OH Leuven</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Cercle Brugge</t>
-        </is>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L153" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M153" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N153" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" t="n">
-        <v>0</v>
-      </c>
-      <c r="T153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="n">
-        <v>0</v>
-      </c>
-      <c r="V153" t="n">
-        <v>0</v>
-      </c>
-      <c r="W153" t="n">
-        <v>0</v>
-      </c>
-      <c r="X153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA153" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB153" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI153" s="3" t="n">
-        <v>46012.63541666666</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Germany 3. Liga</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Viktoria Köln</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>MSV Duisburg</t>
-        </is>
-      </c>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="n">
-        <v>0</v>
-      </c>
-      <c r="T154" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" t="n">
-        <v>0</v>
-      </c>
-      <c r="W154" t="n">
-        <v>0</v>
-      </c>
-      <c r="X154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI154" s="3" t="n">
-        <v>46012.64583333334</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AEK Athens</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>OFI</t>
-        </is>
-      </c>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L155" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M155" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N155" t="n">
-        <v>18</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" t="n">
-        <v>0</v>
-      </c>
-      <c r="W155" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB155" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI155" s="3" t="n">
-        <v>46012.66666666666</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group C</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Siracusa</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Trapani 1905</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L156" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" t="n">
-        <v>0</v>
-      </c>
-      <c r="W156" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI156" s="3" t="n">
-        <v>46012.6875</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group C</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Virtus Casarano</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Team Altamura</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" t="n">
-        <v>0</v>
-      </c>
-      <c r="W157" t="n">
-        <v>0</v>
-      </c>
-      <c r="X157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI157" s="3" t="n">
-        <v>46012.6875</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L158" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M158" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N158" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" t="n">
-        <v>0</v>
-      </c>
-      <c r="W158" t="n">
-        <v>0</v>
-      </c>
-      <c r="X158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB158" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI158" s="3" t="n">
-        <v>46012.69791666666</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" t="n">
-        <v>0</v>
-      </c>
-      <c r="W159" t="n">
-        <v>0</v>
-      </c>
-      <c r="X159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI159" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Treasure Beach</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" t="n">
-        <v>0</v>
-      </c>
-      <c r="X160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI160" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Chapelton</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Cavalier</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI161" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Dunbeholden</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Tivoli Gardens</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" t="n">
-        <v>0</v>
-      </c>
-      <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI162" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI163" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Spain Segunda División</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Cádiz</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>CD Castellón</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L164" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" t="n">
-        <v>0</v>
-      </c>
-      <c r="N164" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="n">
-        <v>0</v>
-      </c>
-      <c r="T164" t="n">
-        <v>0</v>
-      </c>
-      <c r="U164" t="n">
-        <v>0</v>
-      </c>
-      <c r="V164" t="n">
-        <v>0</v>
-      </c>
-      <c r="W164" t="n">
-        <v>0</v>
-      </c>
-      <c r="X164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI164" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Real Betis</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Getafe CF</t>
-        </is>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M165" t="n">
-        <v>0</v>
-      </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="n">
-        <v>0</v>
-      </c>
-      <c r="T165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="n">
-        <v>0</v>
-      </c>
-      <c r="V165" t="n">
-        <v>0</v>
-      </c>
-      <c r="W165" t="n">
-        <v>0</v>
-      </c>
-      <c r="X165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI165" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Santa Clara</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>FC Arouca</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" t="n">
-        <v>0</v>
-      </c>
-      <c r="V166" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" t="n">
-        <v>0</v>
-      </c>
-      <c r="X166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI166" s="3" t="n">
         <v>46012.72916666666</v>
       </c>
     </row>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI125"/>
+  <dimension ref="A1:AI166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46012.39583333334</v>
+        <v>46012.375</v>
       </c>
     </row>
     <row r="19">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46012.40972222222</v>
+        <v>46012.39583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46012.41666666666</v>
+        <v>46012.40972222222</v>
       </c>
     </row>
     <row r="25">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.41666666666</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.41666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.41666666666</v>
       </c>
     </row>
     <row r="32">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="M35" t="n">
         <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,76 +5300,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="42">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="45">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,76 +5776,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="46">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="47">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="48">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="49">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="50">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.49305555555</v>
       </c>
     </row>
     <row r="51">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="80">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="81">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="82">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="83">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="84">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="85">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="86">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="87">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,16 +10819,16 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="88">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="89">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="AI89" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="90">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="AI90" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="91">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11319,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="92">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11438,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="AI92" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="93">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11557,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="AI93" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="94">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
-        <v>46012.55208333334</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="95">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="AI95" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="96">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11914,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="97">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12033,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="AI97" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="98">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12152,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="99">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="AI99" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="100">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12372,10 +12372,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="101">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12509,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="102">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12628,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="103">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
-        <v>46012.57291666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="104">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AI104" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="105">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="107">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="108">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="109">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N109" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="111">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="112">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="113">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="114">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="115">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46012.64583333334</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="116">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.19</v>
+        <v>4</v>
       </c>
       <c r="M116" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="N116" t="n">
-        <v>18</v>
+        <v>1.75</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,17 +14270,17 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD116" t="n">
         <v>1.6</v>
       </c>
-      <c r="AB116" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>0</v>
-      </c>
       <c r="AE116" t="n">
         <v>0</v>
       </c>
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46012.66666666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="117">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="118">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="119">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46012.69791666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="120">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14770,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="121">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="122">
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="123">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="124">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="125">
@@ -15255,116 +15255,4995 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Spain Segunda División RFEF Group 2</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CD Alfaro</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CD Ebro</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" s="3" t="n">
+        <v>46012.54166666666</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Spain Segunda División RFEF Group 2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Real Zaragoza II</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Beasain</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="3" t="n">
+        <v>46012.54166666666</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" s="3" t="n">
+        <v>46012.55208333334</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Lecco</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Pergolettese</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Novara</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ospitaletto</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hungary NB I</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Debrecen</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Várda SE</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Forlì</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Giana Erminio</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>14</v>
+      </c>
+      <c r="M133" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Monopoli</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Potenza Calcio</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" s="3" t="n">
+        <v>46012.5625</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="3" t="n">
+        <v>46012.57291666666</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Kasımpaşa</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" s="3" t="n">
+        <v>46012.58333333334</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Cyprus First Division</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Digenis Ypsonas</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Apollon</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" s="3" t="n">
+        <v>46012.58333333334</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cyprus First Division</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Paphos</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>APOEL</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" s="3" t="n">
+        <v>46012.58333333334</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Göztepe</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="3" t="n">
+        <v>46012.58333333334</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M141" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="3" t="n">
+        <v>46012.58333333334</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M142" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N142" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Albacete Balompié</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" s="3" t="n">
+        <v>46012.60416666666</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Rapid Bucureşti</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M149" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" s="3" t="n">
+        <v>46012.625</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" s="3" t="n">
+        <v>46012.625</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>CD Tondela</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="3" t="n">
+        <v>46012.625</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M152" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N152" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" s="3" t="n">
+        <v>46012.63541666666</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Belgium First Division B</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AS Eupen</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Olympic Charleroi</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" s="3" t="n">
+        <v>46012.63541666666</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Viktoria Köln</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>MSV Duisburg</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" s="3" t="n">
+        <v>46012.64583333334</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M155" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N155" t="n">
+        <v>18</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" s="3" t="n">
+        <v>46012.66666666666</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Siracusa</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Trapani 1905</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" s="3" t="n">
+        <v>46012.6875</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Virtus Casarano</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Team Altamura</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="3" t="n">
+        <v>46012.6875</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M158" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="3" t="n">
+        <v>46012.69791666666</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>CD Castellón</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Chapelton</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>Santa Clara</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>FC Arouca</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="inlineStr">
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" s="3" t="n">
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="3" t="n">
         <v>46012.72916666666</v>
       </c>
     </row>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI166"/>
+  <dimension ref="A1:AI167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
         <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="43">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="49">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
         <v>3.95</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46012.49305555555</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.49305555555</v>
       </c>
     </row>
     <row r="52">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9278,10 +9278,10 @@
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AI104" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="105">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="108">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="115">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="122">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15493,12 +15493,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15603,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="AI127" s="3" t="n">
-        <v>46012.55208333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="128">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15722,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.55208333334</v>
       </c>
     </row>
     <row r="129">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16299,10 +16299,10 @@
         <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16674,7 +16674,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="3" t="n">
-        <v>46012.57291666666</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="137">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.57291666666</v>
       </c>
     </row>
     <row r="138">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17278,12 +17278,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17322,10 +17322,10 @@
         <v>1.95</v>
       </c>
       <c r="M142" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N142" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>0</v>
       </c>
       <c r="AI142" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="143">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18111,12 +18111,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="M149" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N149" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18221,7 +18221,7 @@
         <v>0</v>
       </c>
       <c r="AI149" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="150">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18578,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="153">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>46012.64583333334</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="155">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>46012.66666666666</v>
+        <v>46012.64583333334</v>
       </c>
     </row>
     <row r="156">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.66666666666</v>
       </c>
     </row>
     <row r="157">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>46012.69791666666</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="159">
@@ -19301,12 +19301,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.69791666666</v>
       </c>
     </row>
     <row r="160">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20134,116 +20134,235 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>Santa Clara</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>FC Arouca</t>
         </is>
       </c>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="inlineStr">
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" t="n">
-        <v>0</v>
-      </c>
-      <c r="V166" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" t="n">
-        <v>0</v>
-      </c>
-      <c r="X166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI166" s="3" t="n">
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="3" t="n">
         <v>46012.72916666666</v>
       </c>
     </row>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
         <v>3.95</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
         <v>3.95</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9278,10 +9278,10 @@
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N117" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>2.14</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>7.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
         <v>3.95</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
         <v>3.95</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G165" t="n">

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>7.8</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
         <v>3.95</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
         <v>3.95</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11539,10 +11539,10 @@
         <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="M115" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N115" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD115" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="M121" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N121" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M151" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N151" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="M152" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N152" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,17 +4820,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.05</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="M89" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="N89" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11539,10 +11539,10 @@
         <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N109" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.55</v>
+        <v>1.95</v>
       </c>
       <c r="M146" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N146" t="n">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17953,10 +17953,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="M151" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N151" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M152" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N152" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="M27" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="M89" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="N89" t="n">
-        <v>10.5</v>
+        <v>1.75</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M109" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N109" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>14</v>
+        <v>2.03</v>
       </c>
       <c r="M129" t="n">
-        <v>8.5</v>
+        <v>3.45</v>
       </c>
       <c r="N129" t="n">
-        <v>1.16</v>
+        <v>3.35</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB129" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,16 +16650,16 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD136" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M138" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N138" t="n">
-        <v>1.77</v>
+        <v>3.85</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16891,7 +16891,7 @@
         <v>2.05</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17798,10 +17798,10 @@
         <v>1.95</v>
       </c>
       <c r="M146" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N146" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M147" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N147" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17953,16 +17953,16 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M148" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N148" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18072,16 +18072,16 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M150" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N150" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="M151" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N151" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="M152" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N152" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
         <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N43" t="n">
-        <v>2.18</v>
+        <v>3.64</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46012.45833333334</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="M46" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="N46" t="n">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="M47" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="M49" t="n">
         <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="M109" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N109" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M110" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N110" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB110" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M114" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="N114" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.7</v>
+        <v>3.97</v>
       </c>
       <c r="M120" t="n">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="N120" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD120" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="M128" t="n">
         <v>3.1</v>
       </c>
       <c r="N128" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,16 +16412,16 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD134" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,16 +16650,16 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD136" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE136" t="n">
         <v>0</v>
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="M138" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N138" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="M146" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N146" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M147" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N147" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17953,16 +17953,16 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2</v>
+        <v>2.79</v>
       </c>
       <c r="M148" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N148" t="n">
-        <v>4.1</v>
+        <v>2.23</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18072,16 +18072,16 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="M150" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="N150" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M151" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N151" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M154" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N154" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="M159" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N159" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI167"/>
+  <dimension ref="A1:AI171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46012.39583333334</v>
+        <v>46012.375</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.34</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="N23" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46012.40972222222</v>
+        <v>46012.39583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46012.41666666666</v>
+        <v>46012.40972222222</v>
       </c>
     </row>
     <row r="26">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,61 +4229,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.6</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.41666666666</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46012.4375</v>
+        <v>46012.41666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.02</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.31</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,80 +5653,80 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.4375</v>
       </c>
     </row>
     <row r="45">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="N47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="M48" t="n">
-        <v>4.6</v>
+        <v>2.93</v>
       </c>
       <c r="N48" t="n">
-        <v>6.2</v>
+        <v>3.64</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="N49" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="50">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="N50" t="n">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46012.49305555555</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="52">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="53">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="54">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.49305555555</v>
       </c>
     </row>
     <row r="55">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N96" t="n">
-        <v>2.95</v>
+        <v>2.17</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="107">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="108">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="109">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="M110" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N110" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="111">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,10 +13630,10 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N111" t="n">
         <v>3.2</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="116">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="M116" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="117">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="118">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.97</v>
+        <v>2.73</v>
       </c>
       <c r="M120" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="N120" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="123">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="124">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="125">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15722,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
-        <v>46012.55208333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="129">
@@ -15731,12 +15731,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AI129" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="130">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="AI130" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="131">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.55208333334</v>
       </c>
     </row>
     <row r="133">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,16 +16412,16 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46012.57291666666</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="138">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.07</v>
+        <v>13</v>
       </c>
       <c r="M138" t="n">
-        <v>3.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N138" t="n">
-        <v>3.58</v>
+        <v>1.14</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,16 +16888,16 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="AC138" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD138" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE138" t="n">
         <v>0</v>
@@ -16912,7 +16912,7 @@
         <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="139">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="140">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="141">
@@ -17159,12 +17159,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.57291666666</v>
       </c>
     </row>
     <row r="142">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="144">
@@ -17516,12 +17516,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17626,7 +17626,7 @@
         <v>0</v>
       </c>
       <c r="AI144" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="145">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17745,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="AI145" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="146">
@@ -17754,12 +17754,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17798,10 +17798,10 @@
         <v>2.07</v>
       </c>
       <c r="M146" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N146" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17864,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="AI146" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="147">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17953,10 +17953,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.79</v>
+        <v>1.95</v>
       </c>
       <c r="M148" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N148" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.95</v>
+        <v>2.79</v>
       </c>
       <c r="M149" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N149" t="n">
-        <v>4</v>
+        <v>2.23</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="151">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="M151" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N151" t="n">
-        <v>2.25</v>
+        <v>3.94</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18429,16 +18429,16 @@
         <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18459,7 +18459,7 @@
         <v>0</v>
       </c>
       <c r="AI151" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="152">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18578,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="153">
@@ -18587,12 +18587,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="M153" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N153" t="n">
-        <v>2.47</v>
+        <v>3.89</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18697,7 +18697,7 @@
         <v>0</v>
       </c>
       <c r="AI153" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="154">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="M154" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N154" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="155">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>46012.64583333334</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="156">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.19</v>
+        <v>2.19</v>
       </c>
       <c r="M156" t="n">
-        <v>5.8</v>
+        <v>2.99</v>
       </c>
       <c r="N156" t="n">
-        <v>18</v>
+        <v>3.04</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB156" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>46012.66666666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="157">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19173,7 +19173,7 @@
         <v>0</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="158">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="159">
@@ -19301,12 +19301,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>46012.69791666666</v>
+        <v>46012.64583333334</v>
       </c>
     </row>
     <row r="160">
@@ -19420,12 +19420,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>0</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.66666666666</v>
       </c>
     </row>
     <row r="161">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19649,7 +19649,7 @@
         <v>0</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="162">
@@ -19658,12 +19658,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19768,7 +19768,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="163">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.69791666666</v>
       </c>
     </row>
     <row r="164">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20253,116 +20253,592 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>CD Castellón</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M168" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N168" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI169" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>0</v>
+      </c>
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI170" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>Santa Clara</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>FC Arouca</t>
         </is>
       </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="inlineStr">
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L167" t="n">
+      <c r="L171" t="n">
         <v>1.65</v>
       </c>
-      <c r="M167" t="n">
+      <c r="M171" t="n">
         <v>3.65</v>
       </c>
-      <c r="N167" t="n">
+      <c r="N171" t="n">
         <v>5.2</v>
       </c>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" t="n">
-        <v>0</v>
-      </c>
-      <c r="U167" t="n">
-        <v>0</v>
-      </c>
-      <c r="V167" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" t="n">
-        <v>0</v>
-      </c>
-      <c r="X167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA167" t="n">
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB167" t="n">
+      <c r="AB171" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI167" s="3" t="n">
+      <c r="AC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI171" s="3" t="n">
         <v>46012.72916666666</v>
       </c>
     </row>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI171"/>
+  <dimension ref="A1:AI167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.34</v>
+        <v>3.61</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.61</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M24" t="n">
         <v>3.25</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>3.21</v>
       </c>
       <c r="M28" t="n">
-        <v>3.74</v>
+        <v>3.04</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.21</v>
+        <v>2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="M48" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="N48" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46012.45833333334</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="52">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.49305555555</v>
       </c>
     </row>
     <row r="54">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46012.49305555555</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="55">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="M92" t="n">
         <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.31</v>
+        <v>4.4</v>
       </c>
       <c r="M97" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.39</v>
+        <v>1.23</v>
       </c>
       <c r="M99" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="N99" t="n">
-        <v>2.95</v>
+        <v>9.6</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="108">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.79</v>
+        <v>2.07</v>
       </c>
       <c r="M110" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="N110" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="111">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="M111" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N111" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3</v>
+        <v>3.97</v>
       </c>
       <c r="M117" t="n">
-        <v>3.1</v>
+        <v>3.77</v>
       </c>
       <c r="N117" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,17 +14389,17 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="AB117" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD117" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>0</v>
-      </c>
       <c r="AE117" t="n">
         <v>0</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="118">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.97</v>
+        <v>2.73</v>
       </c>
       <c r="M121" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="N121" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="125">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.55208333334</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46012.55208333334</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="133">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,16 +16769,16 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD137" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>13</v>
+        <v>2.02</v>
       </c>
       <c r="M138" t="n">
-        <v>8.300000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="N138" t="n">
-        <v>1.14</v>
+        <v>3.45</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,16 +16888,16 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AB138" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC138" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE138" t="n">
         <v>0</v>
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="141">
@@ -17159,12 +17159,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46012.57291666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="142">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="144">
@@ -17516,12 +17516,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17626,7 +17626,7 @@
         <v>0</v>
       </c>
       <c r="AI144" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="145">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17745,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="AI145" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="146">
@@ -17754,12 +17754,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17864,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="AI146" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="147">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17953,10 +17953,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="151">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="M151" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="N151" t="n">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18429,16 +18429,16 @@
         <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18459,7 +18459,7 @@
         <v>0</v>
       </c>
       <c r="AI151" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="152">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18578,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="153">
@@ -18587,12 +18587,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="M153" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="N153" t="n">
-        <v>3.89</v>
+        <v>4.6</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18697,7 +18697,7 @@
         <v>0</v>
       </c>
       <c r="AI153" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="154">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M154" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="N154" t="n">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="155">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.64583333334</v>
       </c>
     </row>
     <row r="156">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.19</v>
+        <v>1.19</v>
       </c>
       <c r="M156" t="n">
-        <v>2.99</v>
+        <v>5.8</v>
       </c>
       <c r="N156" t="n">
-        <v>3.04</v>
+        <v>18</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.66666666666</v>
       </c>
     </row>
     <row r="157">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19173,7 +19173,7 @@
         <v>0</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="158">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="159">
@@ -19301,12 +19301,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>46012.64583333334</v>
+        <v>46012.69791666666</v>
       </c>
     </row>
     <row r="160">
@@ -19420,12 +19420,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>0</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>46012.66666666666</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="161">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19649,7 +19649,7 @@
         <v>0</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="162">
@@ -19658,12 +19658,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19768,7 +19768,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="163">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>46012.69791666666</v>
+        <v>46012.70833333334</v>
       </c>
     </row>
     <row r="164">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20253,12 +20253,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20363,482 +20363,6 @@
         <v>0</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Spain Segunda División</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Cádiz</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>CD Castellón</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M168" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N168" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="n">
-        <v>0</v>
-      </c>
-      <c r="T168" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" t="n">
-        <v>0</v>
-      </c>
-      <c r="W168" t="n">
-        <v>0</v>
-      </c>
-      <c r="X168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA168" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB168" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI168" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="G169" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L169" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" t="n">
-        <v>0</v>
-      </c>
-      <c r="N169" t="n">
-        <v>0</v>
-      </c>
-      <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
-      <c r="S169" t="n">
-        <v>0</v>
-      </c>
-      <c r="T169" t="n">
-        <v>0</v>
-      </c>
-      <c r="U169" t="n">
-        <v>0</v>
-      </c>
-      <c r="V169" t="n">
-        <v>0</v>
-      </c>
-      <c r="W169" t="n">
-        <v>0</v>
-      </c>
-      <c r="X169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI169" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="G170" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" t="n">
-        <v>0</v>
-      </c>
-      <c r="I170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L170" t="n">
-        <v>0</v>
-      </c>
-      <c r="M170" t="n">
-        <v>0</v>
-      </c>
-      <c r="N170" t="n">
-        <v>0</v>
-      </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="n">
-        <v>0</v>
-      </c>
-      <c r="T170" t="n">
-        <v>0</v>
-      </c>
-      <c r="U170" t="n">
-        <v>0</v>
-      </c>
-      <c r="V170" t="n">
-        <v>0</v>
-      </c>
-      <c r="W170" t="n">
-        <v>0</v>
-      </c>
-      <c r="X170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI170" s="3" t="n">
-        <v>46012.70833333334</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Santa Clara</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>FC Arouca</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
-        <v>0</v>
-      </c>
-      <c r="H171" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L171" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M171" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N171" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" t="n">
-        <v>0</v>
-      </c>
-      <c r="T171" t="n">
-        <v>0</v>
-      </c>
-      <c r="U171" t="n">
-        <v>0</v>
-      </c>
-      <c r="V171" t="n">
-        <v>0</v>
-      </c>
-      <c r="W171" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA171" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB171" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI171" s="3" t="n">
         <v>46012.72916666666</v>
       </c>
     </row>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI167"/>
+  <dimension ref="A1:AI171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC12" t="n">
         <v>2.08</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>2.91</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.61</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M21" t="n">
         <v>3.25</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.34</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="N24" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.05</v>
+        <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,76 +6490,76 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46012.47916666666</v>
+        <v>46012.45833333334</v>
       </c>
     </row>
     <row r="52">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46012.49305555555</v>
+        <v>46012.47916666666</v>
       </c>
     </row>
     <row r="54">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46012.5</v>
+        <v>46012.49305555555</v>
       </c>
     </row>
     <row r="55">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.29</v>
+        <v>4.4</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,16 +12842,16 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46012.51041666666</v>
+        <v>46012.5</v>
       </c>
     </row>
     <row r="108">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="M108" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46012.52083333334</v>
+        <v>46012.51041666666</v>
       </c>
     </row>
     <row r="111">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M113" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N113" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="M115" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N115" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.97</v>
+        <v>2.05</v>
       </c>
       <c r="M117" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46012.53125</v>
+        <v>46012.52083333334</v>
       </c>
     </row>
     <row r="118">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46012.54166666666</v>
+        <v>46012.53125</v>
       </c>
     </row>
     <row r="125">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46012.55208333334</v>
+        <v>46012.54166666666</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46012.5625</v>
+        <v>46012.55208333334</v>
       </c>
     </row>
     <row r="133">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,14 +16486,14 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="M135" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N135" t="n">
         <v>3.45</v>
       </c>
-      <c r="N135" t="n">
-        <v>3.35</v>
-      </c>
       <c r="O135" t="n">
         <v>0</v>
       </c>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,16 +16769,16 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.5625</v>
       </c>
     </row>
     <row r="141">
@@ -17159,12 +17159,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46012.58333333334</v>
+        <v>46012.57291666666</v>
       </c>
     </row>
     <row r="142">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="144">
@@ -17516,12 +17516,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M144" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>1.77</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17626,7 +17626,7 @@
         <v>0</v>
       </c>
       <c r="AI144" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="145">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.79</v>
+        <v>2.07</v>
       </c>
       <c r="M145" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N145" t="n">
-        <v>2.23</v>
+        <v>3.58</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17745,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="AI145" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="146">
@@ -17754,12 +17754,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17864,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="AI146" s="3" t="n">
-        <v>46012.60416666666</v>
+        <v>46012.58333333334</v>
       </c>
     </row>
     <row r="147">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17953,10 +17953,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18072,16 +18072,16 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="M150" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N150" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="151">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18459,7 +18459,7 @@
         <v>0</v>
       </c>
       <c r="AI151" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="152">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="M152" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N152" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18578,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>46012.625</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="153">
@@ -18587,12 +18587,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18697,7 +18697,7 @@
         <v>0</v>
       </c>
       <c r="AI153" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.60416666666</v>
       </c>
     </row>
     <row r="154">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="M154" t="n">
-        <v>3.27</v>
+        <v>2.99</v>
       </c>
       <c r="N154" t="n">
-        <v>2.47</v>
+        <v>3.04</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>46012.63541666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="155">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>46012.64583333334</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="156">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.19</v>
+        <v>2.95</v>
       </c>
       <c r="M156" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>18</v>
+        <v>2.25</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB156" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>46012.66666666666</v>
+        <v>46012.625</v>
       </c>
     </row>
     <row r="157">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19173,7 +19173,7 @@
         <v>0</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="158">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>46012.6875</v>
+        <v>46012.63541666666</v>
       </c>
     </row>
     <row r="159">
@@ -19301,12 +19301,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>46012.69791666666</v>
+        <v>46012.64583333334</v>
       </c>
     </row>
     <row r="160">
@@ -19420,12 +19420,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>0</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.66666666666</v>
       </c>
     </row>
     <row r="161">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19649,7 +19649,7 @@
         <v>0</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="162">
@@ -19658,12 +19658,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19768,7 +19768,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.6875</v>
       </c>
     </row>
     <row r="163">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>46012.70833333334</v>
+        <v>46012.69791666666</v>
       </c>
     </row>
     <row r="164">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20253,116 +20253,592 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI169" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Chapelton</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>0</v>
+      </c>
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI170" s="3" t="n">
+        <v>46012.70833333334</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>Santa Clara</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>FC Arouca</t>
         </is>
       </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="inlineStr">
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L167" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M167" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N167" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" t="n">
-        <v>0</v>
-      </c>
-      <c r="U167" t="n">
-        <v>0</v>
-      </c>
-      <c r="V167" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" t="n">
-        <v>0</v>
-      </c>
-      <c r="X167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA167" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB167" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI167" s="3" t="n">
+      <c r="L171" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M171" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N171" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI171" s="3" t="n">
         <v>46012.72916666666</v>
       </c>
     </row>

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>2.91</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.34</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>3.34</v>
       </c>
       <c r="M24" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>2.16</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>3.21</v>
       </c>
       <c r="M27" t="n">
-        <v>3.74</v>
+        <v>3.04</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.47</v>
+        <v>3.74</v>
       </c>
       <c r="N32" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="M45" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.64</v>
+        <v>2.18</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="M46" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="M48" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N50" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6493,70 +6493,70 @@
         <v>2.2</v>
       </c>
       <c r="M51" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,55 +6609,55 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
         <v>1.98</v>
       </c>
-      <c r="M52" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N53" t="n">
-        <v>4.33</v>
+        <v>3.47</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="M87" t="n">
         <v>2.85</v>
       </c>
       <c r="N87" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="M88" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,16 +11295,16 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,16 +12842,16 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M111" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N111" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="M113" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N113" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="M114" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.03</v>
+        <v>13</v>
       </c>
       <c r="M139" t="n">
-        <v>3.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N139" t="n">
-        <v>3.35</v>
+        <v>1.14</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,16 +17007,16 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD139" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18072,16 +18072,16 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="M150" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N150" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.79</v>
+        <v>1.95</v>
       </c>
       <c r="M152" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N152" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18667,16 +18667,16 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="M154" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N154" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="M155" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="N155" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="M156" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N156" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G170" t="n">

--- a/jogos_2025-12-21.xlsx
+++ b/jogos_2025-12-21.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="M17" t="n">
-        <v>2.91</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>2.91</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N45" t="n">
-        <v>2.18</v>
+        <v>3.64</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="M46" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="N46" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="M47" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.43</v>
+        <v>3.45</v>
       </c>
       <c r="M48" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N48" t="n">
-        <v>6.2</v>
+        <v>2.04</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N50" t="n">
-        <v>2.04</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46012.45833333334</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N89" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,16 +11295,16 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.3</v>
+        <v>2.39</v>
       </c>
       <c r="M95" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N95" t="n">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,16 +12366,16 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="N108" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,16 +15222,16 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,16 +16769,16 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD137" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,16 +17007,16 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD139" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4.6</v>
+        <v>2.07</v>
       </c>
       <c r="M143" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N143" t="n">
-        <v>1.77</v>
+        <v>3.58</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17486,7 +17486,7 @@
         <v>2.05</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18072,16 +18072,16 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
    